--- a/examples/exports/每日晨读会-示例-20260302.xlsx
+++ b/examples/exports/每日晨读会-示例-20260302.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t xml:space="preserve">会议主题:</t>
   </si>
@@ -25,7 +25,7 @@
     <t xml:space="preserve">会议创建者:</t>
   </si>
   <si>
-    <t xml:space="preserve">晨光</t>
+    <t xml:space="preserve">A001</t>
   </si>
   <si>
     <t xml:space="preserve">预定开始时间:</t>
@@ -73,193 +73,187 @@
     <t xml:space="preserve">2026-03-02 05:40:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-02 07:00:14</t>
+    <t xml:space="preserve">2026-03-02 07:00:28</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">80分钟14秒</t>
+    <t xml:space="preserve">80分钟28秒</t>
   </si>
   <si>
     <t xml:space="preserve">主持人</t>
   </si>
   <si>
-    <t xml:space="preserve">小满</t>
+    <t xml:space="preserve">A002</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-02 05:45:10</t>
   </si>
   <si>
-    <t xml:space="preserve">75分钟4秒</t>
+    <t xml:space="preserve">75分钟18秒</t>
   </si>
   <si>
     <t xml:space="preserve">参会者</t>
   </si>
   <si>
-    <t xml:space="preserve">知夏</t>
+    <t xml:space="preserve">A011</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-02 05:46:58</t>
   </si>
   <si>
-    <t xml:space="preserve">73分钟16秒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">麦穗</t>
+    <t xml:space="preserve">73分钟30秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A005</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-02 05:48:45</t>
   </si>
   <si>
-    <t xml:space="preserve">71分钟29秒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">安安</t>
+    <t xml:space="preserve">71分钟43秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A014</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-02 05:51:07</t>
   </si>
   <si>
-    <t xml:space="preserve">69分钟7秒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海盐（上海）</t>
+    <t xml:space="preserve">69分钟21秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A003（上海）</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-02 05:52:31</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-03-02 07:00:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68分钟25秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A010（二组）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-02 05:53:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67分钟16秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a015-广州</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-02 05:54:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-02 07:00:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66分钟5秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A004(三组)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-02 05:55:02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65分钟54秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A012家长</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-02 05:56:15</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-03-02 07:00:42</t>
   </si>
   <si>
-    <t xml:space="preserve">68分钟11秒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">南风（李）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-02 05:53:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-02 07:00:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66分钟55秒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LILY-广州</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-02 05:54:44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-02 07:00:49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66分钟5秒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">小鹿(三组)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-02 05:55:02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65分钟40秒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">布丁妈妈</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-02 05:56:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-02 07:00:28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64分钟13秒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">山茶花</t>
+    <t xml:space="preserve">64分钟27秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A006-平板</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-02 05:57:20</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-02 07:00:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63分钟1秒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">七七</t>
+    <t xml:space="preserve">63分钟29秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A017</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-02 05:57:57</t>
   </si>
   <si>
-    <t xml:space="preserve">62分钟17秒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abu</t>
+    <t xml:space="preserve">62分钟31秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a007</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-02 05:58:03</t>
   </si>
   <si>
-    <t xml:space="preserve">62分钟18秒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一一</t>
+    <t xml:space="preserve">62分钟25秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A018</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-02 05:58:30</t>
   </si>
   <si>
-    <t xml:space="preserve">61分钟44秒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">旧书签</t>
+    <t xml:space="preserve">61分钟58秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A019</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-02 05:59:00</t>
   </si>
   <si>
-    <t xml:space="preserve">61分钟21秒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">青柠-手机</t>
+    <t xml:space="preserve">61分钟28秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A008-手机</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-02 05:59:30</t>
   </si>
   <si>
-    <t xml:space="preserve">61分钟5秒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kevin(Zhang)</t>
+    <t xml:space="preserve">61分钟19秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A016(北京)</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-02 06:00:01</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-02 07:01:24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61分钟23秒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一一的iPad</t>
+    <t xml:space="preserve">60分钟55秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A018的iPad</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-02 06:02:00</t>
   </si>
   <si>
-    <t xml:space="preserve">58分钟49秒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">木木</t>
+    <t xml:space="preserve">2026-03-02 07:01:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59分钟3秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A009</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-02 07:05:00</t>
@@ -512,13 +506,13 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" t="s">
         <v>44</v>
-      </c>
-      <c r="D16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" t="s">
-        <v>45</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -526,19 +520,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s">
         <v>46</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>47</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" t="s">
         <v>48</v>
-      </c>
-      <c r="D17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" t="s">
-        <v>49</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -546,10 +540,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" t="s">
         <v>50</v>
-      </c>
-      <c r="B18" t="s">
-        <v>51</v>
       </c>
       <c r="C18" t="s">
         <v>40</v>
@@ -558,7 +552,7 @@
         <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -566,19 +560,19 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
         <v>53</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>54</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" t="s">
         <v>55</v>
-      </c>
-      <c r="D19" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" t="s">
-        <v>56</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -586,19 +580,19 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
         <v>57</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" t="s">
         <v>58</v>
-      </c>
-      <c r="C20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" t="s">
-        <v>60</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -606,19 +600,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" t="s">
         <v>61</v>
-      </c>
-      <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" t="s">
-        <v>63</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -626,19 +620,19 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" t="s">
         <v>64</v>
-      </c>
-      <c r="B22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" t="s">
-        <v>66</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -646,19 +640,19 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" t="s">
         <v>67</v>
-      </c>
-      <c r="B23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" t="s">
-        <v>69</v>
       </c>
       <c r="F23" t="s">
         <v>28</v>
@@ -666,19 +660,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" t="s">
         <v>70</v>
-      </c>
-      <c r="B24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" t="s">
-        <v>72</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -686,19 +680,19 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" t="s">
         <v>73</v>
-      </c>
-      <c r="B25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" t="s">
-        <v>75</v>
       </c>
       <c r="F25" t="s">
         <v>28</v>
@@ -706,19 +700,19 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" t="s">
         <v>76</v>
-      </c>
-      <c r="B26" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" t="s">
-        <v>79</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -726,19 +720,19 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" t="s">
         <v>80</v>
-      </c>
-      <c r="B27" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" t="s">
-        <v>82</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
@@ -746,19 +740,19 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" t="s">
         <v>83</v>
-      </c>
-      <c r="B28" t="s">
-        <v>84</v>
-      </c>
-      <c r="C28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" t="s">
-        <v>85</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
